--- a/artfynd/A 35760-2025 artfynd.xlsx
+++ b/artfynd/A 35760-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY12"/>
+  <dimension ref="A1:AY9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,53 +675,48 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>160105</v>
+        <v>305726</v>
       </c>
       <c r="B2" t="n">
-        <v>78839</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91892</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>226</v>
+        <v>883</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Skuggorangelav</t>
+          <t>Kärnticka</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Caloplaca lucifuga</t>
+          <t>Inocutis dryophila</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>G.Thor</t>
+          <t>(Berk.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I2" t="inlineStr"/>
       <c r="P2" t="inlineStr">
         <is>
-          <t>LERBOGA, Ög</t>
+          <t>Ekhage vid Östergården, Lerboga, Ög</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>549050.3687422087</v>
+        <v>549016</v>
       </c>
       <c r="R2" t="n">
-        <v>6471287.073150981</v>
+        <v>6471209</v>
       </c>
       <c r="S2" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -745,22 +740,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="Z2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-15</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AB2" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-15</t>
+        </is>
+      </c>
+      <c r="AC2" t="inlineStr">
+        <is>
+          <t>Observatör: Tomas Fasth</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -772,35 +762,29 @@
       <c r="AG2" t="b">
         <v>0</v>
       </c>
-      <c r="AR2" t="inlineStr"/>
       <c r="AT2" t="inlineStr"/>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Linköpings Kommun (hl)</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>Anders Tingvall</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
+          <t>Naturvårdsprogram för Linköpings kommun</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>152572</v>
+        <v>341136</v>
       </c>
       <c r="B3" t="n">
-        <v>77955</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>92510</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -808,37 +792,37 @@
         </is>
       </c>
       <c r="E3" t="n">
-        <v>374</v>
+        <v>1143</v>
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>Gul dropplav</t>
+          <t>Blekticka</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
         <is>
-          <t>Cliostomum corrugatum</t>
+          <t>Haploporus tuberculosus</t>
         </is>
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>(Ach.:Fr.) Fr.</t>
+          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
-          <t>LERBOGA, Ög</t>
+          <t>Ekhage vid Östergården, Lerboga, Ög</t>
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>549050.3687422087</v>
+        <v>549081</v>
       </c>
       <c r="R3" t="n">
-        <v>6471287.073150981</v>
+        <v>6471290</v>
       </c>
       <c r="S3" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -862,22 +846,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-15</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2010-10-15</t>
+        </is>
+      </c>
+      <c r="AC3" t="inlineStr">
+        <is>
+          <t>Observatör: Tomas Fasth</t>
         </is>
       </c>
       <c r="AD3" t="b">
@@ -889,73 +868,67 @@
       <c r="AG3" t="b">
         <v>0</v>
       </c>
-      <c r="AR3" t="inlineStr"/>
       <c r="AT3" t="inlineStr"/>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Linköpings Kommun (hl)</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>Anders Tingvall</t>
+          <t>Tomas Fasth</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
+          <t>Naturvårdsprogram för Linköpings kommun</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
-        <v>137349</v>
+        <v>612426</v>
       </c>
       <c r="B4" t="n">
-        <v>76918</v>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>104620</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>CR</t>
         </is>
       </c>
       <c r="E4" t="n">
-        <v>218</v>
+        <v>1563</v>
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>Ekspik</t>
+          <t>Bohuslind</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
         <is>
-          <t>Calicium quercinum</t>
+          <t>Tilia platyphyllos</t>
         </is>
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>Pers.</t>
+          <t>Scop.</t>
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
-          <t>LERBOGA, Ög</t>
+          <t>Lerboga 160 m ONO, Ög</t>
         </is>
       </c>
       <c r="Q4" t="n">
-        <v>549050.3687422087</v>
+        <v>548978</v>
       </c>
       <c r="R4" t="n">
-        <v>6471287.073150981</v>
+        <v>6471189</v>
       </c>
       <c r="S4" t="n">
-        <v>100</v>
+        <v>50</v>
       </c>
       <c r="T4" t="inlineStr">
         <is>
@@ -979,22 +952,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>1992-01-01</t>
-        </is>
-      </c>
-      <c r="Z4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-30</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>1993-12-31</t>
-        </is>
-      </c>
-      <c r="AB4" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-30</t>
+        </is>
+      </c>
+      <c r="AC4" t="inlineStr">
+        <is>
+          <t>självsådda buskar</t>
         </is>
       </c>
       <c r="AD4" t="b">
@@ -1006,35 +974,30 @@
       <c r="AG4" t="b">
         <v>0</v>
       </c>
-      <c r="AR4" t="inlineStr"/>
+      <c r="AI4" t="inlineStr">
+        <is>
+          <t>lövskogsbrant</t>
+        </is>
+      </c>
       <c r="AT4" t="inlineStr"/>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>Tommy Karlsson</t>
+          <t>Janne Andersson</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>Anders Tingvall</t>
-        </is>
-      </c>
-      <c r="AY4" t="inlineStr">
-        <is>
-          <t>Sällsynta lavar i Östergötland 2000</t>
-        </is>
-      </c>
+          <t>Janne Andersson</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="n">
         <v>1563681</v>
       </c>
       <c r="B5" t="n">
-        <v>89349</v>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1066,10 +1029,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>549037.8563348134</v>
+        <v>549038</v>
       </c>
       <c r="R5" t="n">
-        <v>6471237.095095436</v>
+        <v>6471237</v>
       </c>
       <c r="S5" t="n">
         <v>100</v>
@@ -1099,19 +1062,9 @@
           <t>2008-10-19</t>
         </is>
       </c>
-      <c r="Z5" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA5" t="inlineStr">
         <is>
           <t>2008-10-19</t>
-        </is>
-      </c>
-      <c r="AB5" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1148,15 +1101,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>341136</v>
+        <v>1570452</v>
       </c>
       <c r="B6" t="n">
-        <v>89953</v>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>91867</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1164,21 +1112,21 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1143</v>
+        <v>5445</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Blekticka</t>
+          <t>Ekticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Haploporus tuberculosus</t>
+          <t>Fomitiporia robusta</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Fr.) Niemelä &amp; Y.C.Dai</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
@@ -1188,10 +1136,10 @@
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>549081.3370293829</v>
+        <v>549012</v>
       </c>
       <c r="R6" t="n">
-        <v>6471289.557093117</v>
+        <v>6471271</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1221,19 +1169,9 @@
           <t>2010-10-15</t>
         </is>
       </c>
-      <c r="Z6" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA6" t="inlineStr">
         <is>
           <t>2010-10-15</t>
-        </is>
-      </c>
-      <c r="AB6" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC6" t="inlineStr">
@@ -1269,53 +1207,48 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>1570452</v>
+        <v>3511756</v>
       </c>
       <c r="B7" t="n">
-        <v>89350</v>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>106813</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>EN</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>5445</v>
+        <v>220785</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Ekticka</t>
+          <t>Ask</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Fomitiporia robusta</t>
+          <t>Fraxinus excelsior</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Ekhage vid Östergården, Lerboga, Ög</t>
+          <t>Lerboga 160 m ONO, Ög</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>549011.6902930996</v>
+        <v>548978</v>
       </c>
       <c r="R7" t="n">
-        <v>6471270.857939865</v>
+        <v>6471189</v>
       </c>
       <c r="S7" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T7" t="inlineStr">
         <is>
@@ -1339,27 +1272,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2010-10-15</t>
-        </is>
-      </c>
-      <c r="Z7" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-08</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>2010-10-15</t>
-        </is>
-      </c>
-      <c r="AB7" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC7" t="inlineStr">
-        <is>
-          <t>Observatör: Tomas Fasth</t>
+          <t>2012-04-08</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1370,73 +1288,69 @@
       </c>
       <c r="AG7" t="b">
         <v>0</v>
+      </c>
+      <c r="AI7" t="inlineStr">
+        <is>
+          <t>lövskogsbrant</t>
+        </is>
       </c>
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Linköpings Kommun (hl)</t>
+          <t>Janne Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY7" t="inlineStr">
-        <is>
-          <t>Naturvårdsprogram för Linköpings kommun</t>
-        </is>
-      </c>
+          <t>Janne Andersson</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>305726</v>
+        <v>4957977</v>
       </c>
       <c r="B8" t="n">
-        <v>89375</v>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>101326</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>883</v>
+        <v>222498</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Kärnticka</t>
+          <t>Blåsippa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Inocutis dryophila</t>
+          <t>Hepatica nobilis</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Berk.) Fiasson &amp; Niemelä</t>
+          <t>Schreb.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Ekhage vid Östergården, Lerboga, Ög</t>
+          <t>Lerboga 160 m ONO, Ög</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>549015.6130740542</v>
+        <v>548978</v>
       </c>
       <c r="R8" t="n">
-        <v>6471209.022188812</v>
+        <v>6471189</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>50</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1460,27 +1374,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2010-10-15</t>
-        </is>
-      </c>
-      <c r="Z8" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-04-08</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>2010-10-15</t>
-        </is>
-      </c>
-      <c r="AB8" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC8" t="inlineStr">
-        <is>
-          <t>Observatör: Tomas Fasth</t>
+          <t>2012-04-08</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1491,59 +1390,51 @@
       </c>
       <c r="AG8" t="b">
         <v>0</v>
+      </c>
+      <c r="AI8" t="inlineStr">
+        <is>
+          <t>lövskogsbrant</t>
+        </is>
       </c>
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Linköpings Kommun (hl)</t>
+          <t>Janne Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Tomas Fasth</t>
-        </is>
-      </c>
-      <c r="AY8" t="inlineStr">
-        <is>
-          <t>Naturvårdsprogram för Linköpings kommun</t>
-        </is>
-      </c>
+          <t>Janne Andersson</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>4957977</v>
+        <v>6353176</v>
       </c>
       <c r="B9" t="n">
-        <v>98520</v>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
+        <v>101746</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>222498</v>
+        <v>224932</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Blåsippa</t>
+          <t>Vanlig backsmörblomma</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Hepatica nobilis</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>Schreb.</t>
-        </is>
-      </c>
+          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr"/>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
@@ -1551,10 +1442,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>548977.5112736494</v>
+        <v>548978</v>
       </c>
       <c r="R9" t="n">
-        <v>6471188.618585223</v>
+        <v>6471189</v>
       </c>
       <c r="S9" t="n">
         <v>50</v>
@@ -1581,22 +1472,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2012-04-08</t>
-        </is>
-      </c>
-      <c r="Z9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-30</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>2012-04-08</t>
-        </is>
-      </c>
-      <c r="AB9" t="inlineStr">
-        <is>
-          <t>00:00</t>
+          <t>2012-05-30</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1625,358 +1506,6 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
-    </row>
-    <row r="10">
-      <c r="A10" t="n">
-        <v>6353176</v>
-      </c>
-      <c r="B10" t="n">
-        <v>98932</v>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>NT</t>
-        </is>
-      </c>
-      <c r="E10" t="n">
-        <v>224932</v>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>Vanlig backsmörblomma</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>Ranunculus polyanthemos subsp. polyanthemos</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr"/>
-      <c r="I10" t="inlineStr"/>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>Lerboga 160 m ONO, Ög</t>
-        </is>
-      </c>
-      <c r="Q10" t="n">
-        <v>548977.5112736494</v>
-      </c>
-      <c r="R10" t="n">
-        <v>6471188.618585223</v>
-      </c>
-      <c r="S10" t="n">
-        <v>50</v>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>Linköping</t>
-        </is>
-      </c>
-      <c r="V10" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W10" t="inlineStr">
-        <is>
-          <t>Bankekind</t>
-        </is>
-      </c>
-      <c r="Y10" t="inlineStr">
-        <is>
-          <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="Z10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA10" t="inlineStr">
-        <is>
-          <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="AB10" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG10" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI10" t="inlineStr">
-        <is>
-          <t>lövskogsbrant</t>
-        </is>
-      </c>
-      <c r="AT10" t="inlineStr"/>
-      <c r="AW10" t="inlineStr">
-        <is>
-          <t>Janne Andersson</t>
-        </is>
-      </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>Janne Andersson</t>
-        </is>
-      </c>
-      <c r="AY10" t="inlineStr"/>
-    </row>
-    <row r="11">
-      <c r="A11" t="n">
-        <v>612426</v>
-      </c>
-      <c r="B11" t="n">
-        <v>101672</v>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CR</t>
-        </is>
-      </c>
-      <c r="E11" t="n">
-        <v>1563</v>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>Bohuslind</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>Tilia platyphyllos</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>Scop.</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>Lerboga 160 m ONO, Ög</t>
-        </is>
-      </c>
-      <c r="Q11" t="n">
-        <v>548977.5112736494</v>
-      </c>
-      <c r="R11" t="n">
-        <v>6471188.618585223</v>
-      </c>
-      <c r="S11" t="n">
-        <v>50</v>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>Linköping</t>
-        </is>
-      </c>
-      <c r="V11" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W11" t="inlineStr">
-        <is>
-          <t>Bankekind</t>
-        </is>
-      </c>
-      <c r="Y11" t="inlineStr">
-        <is>
-          <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="Z11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA11" t="inlineStr">
-        <is>
-          <t>2012-05-30</t>
-        </is>
-      </c>
-      <c r="AB11" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC11" t="inlineStr">
-        <is>
-          <t>självsådda buskar</t>
-        </is>
-      </c>
-      <c r="AD11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG11" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI11" t="inlineStr">
-        <is>
-          <t>lövskogsbrant</t>
-        </is>
-      </c>
-      <c r="AT11" t="inlineStr"/>
-      <c r="AW11" t="inlineStr">
-        <is>
-          <t>Janne Andersson</t>
-        </is>
-      </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>Janne Andersson</t>
-        </is>
-      </c>
-      <c r="AY11" t="inlineStr"/>
-    </row>
-    <row r="12">
-      <c r="A12" t="n">
-        <v>3511756</v>
-      </c>
-      <c r="B12" t="n">
-        <v>103813</v>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>Godkänd baserat på observatörens uppgifter</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>EN</t>
-        </is>
-      </c>
-      <c r="E12" t="n">
-        <v>220785</v>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>Ask</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>Fraxinus excelsior</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr"/>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>Lerboga 160 m ONO, Ög</t>
-        </is>
-      </c>
-      <c r="Q12" t="n">
-        <v>548977.5112736494</v>
-      </c>
-      <c r="R12" t="n">
-        <v>6471188.618585223</v>
-      </c>
-      <c r="S12" t="n">
-        <v>50</v>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>Linköping</t>
-        </is>
-      </c>
-      <c r="V12" t="inlineStr">
-        <is>
-          <t>Östergötland</t>
-        </is>
-      </c>
-      <c r="W12" t="inlineStr">
-        <is>
-          <t>Bankekind</t>
-        </is>
-      </c>
-      <c r="Y12" t="inlineStr">
-        <is>
-          <t>2012-04-08</t>
-        </is>
-      </c>
-      <c r="Z12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AA12" t="inlineStr">
-        <is>
-          <t>2012-04-08</t>
-        </is>
-      </c>
-      <c r="AB12" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AD12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AE12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AG12" t="b">
-        <v>0</v>
-      </c>
-      <c r="AI12" t="inlineStr">
-        <is>
-          <t>lövskogsbrant</t>
-        </is>
-      </c>
-      <c r="AT12" t="inlineStr"/>
-      <c r="AW12" t="inlineStr">
-        <is>
-          <t>Janne Andersson</t>
-        </is>
-      </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>Janne Andersson</t>
-        </is>
-      </c>
-      <c r="AY12" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 35760-2025 artfynd.xlsx
+++ b/artfynd/A 35760-2025 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY9"/>
+  <dimension ref="A1:AZ9"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -778,6 +783,11 @@
           <t>Naturvårdsprogram för Linköpings kommun</t>
         </is>
       </c>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/305726</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -884,6 +894,11 @@
           <t>Naturvårdsprogram för Linköpings kommun</t>
         </is>
       </c>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/341136</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/612426</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1098,6 +1118,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1563681</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1204,6 +1229,11 @@
           <t>Naturvårdsprogram för Linköpings kommun</t>
         </is>
       </c>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/1570452</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1306,6 +1336,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/3511756</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1408,6 +1443,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/4957977</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1506,8 +1546,23 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/6353176</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>